--- a/TT2026 Walking Quantification.xlsx
+++ b/TT2026 Walking Quantification.xlsx
@@ -1,28 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ithacaedu-my.sharepoint.com/personal/iwoods_ithaca_edu/Documents/Desktop/tarditracks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_E05EFDE08085FF9075DE2FBF335F4849B20072D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62916D5D-114F-584A-9FB1-EB51D416FAA1}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="11_E05EFDE08085FF9075DE2FBF335F4849B20072D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF3AC3C-6AB2-4645-AE86-413FC7B9466E}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17400" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="40360" windowHeight="17760" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="demo" sheetId="1" r:id="rId1"/>
-    <sheet name="Group1 - slow walk" sheetId="2" r:id="rId2"/>
-    <sheet name="Group1 - fast walk" sheetId="3" r:id="rId3"/>
-    <sheet name="Group1 - slow run" sheetId="4" r:id="rId4"/>
+    <sheet name="Group1 - slow walk" sheetId="2" r:id="rId1"/>
+    <sheet name="Group1 - fast walk" sheetId="3" r:id="rId2"/>
+    <sheet name="Group1 - slow run" sheetId="4" r:id="rId3"/>
+    <sheet name="Group 1 - fast run" sheetId="11" r:id="rId4"/>
     <sheet name="Group2 - slow walk" sheetId="5" r:id="rId5"/>
     <sheet name="Group2 - fast walk" sheetId="6" r:id="rId6"/>
     <sheet name="Group2 - slow run" sheetId="7" r:id="rId7"/>
-    <sheet name="Group3 - slow walk" sheetId="8" r:id="rId8"/>
-    <sheet name="Group3 - fast walk" sheetId="9" r:id="rId9"/>
-    <sheet name="Group3 - slow run" sheetId="10" r:id="rId10"/>
+    <sheet name="Group2 - fast run" sheetId="12" r:id="rId8"/>
+    <sheet name="Group3 - slow walk" sheetId="8" r:id="rId9"/>
+    <sheet name="Group3 - fast walk" sheetId="9" r:id="rId10"/>
+    <sheet name="Group3 - slow run" sheetId="10" r:id="rId11"/>
+    <sheet name="Group3 - fast run" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="21">
   <si>
     <t>Left DOWN</t>
   </si>
@@ -111,7 +113,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -147,8 +149,23 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -165,12 +182,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFCFE2F3"/>
         <bgColor rgb="FFCFE2F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -192,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -202,9 +213,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -419,11 +431,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.6640625" customWidth="1"/>
@@ -434,11 +446,10 @@
     <col min="6" max="6" width="8" customWidth="1"/>
     <col min="7" max="7" width="17.6640625" customWidth="1"/>
     <col min="8" max="8" width="18.5" customWidth="1"/>
-    <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="17.1640625" customWidth="1"/>
+    <col min="9" max="9" width="49.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -463,120 +474,236 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="4">
         <v>7.2766999999999999</v>
       </c>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
       <c r="F2" s="4">
         <v>6.6703000000000001</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="I2" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4">
         <v>7.7145999999999999</v>
       </c>
       <c r="B3" s="4">
         <v>8.5230999999999995</v>
       </c>
+      <c r="C3" s="4">
+        <f t="shared" ref="C3:C8" si="0">A4-A3</f>
+        <v>1.2128000000000005</v>
+      </c>
+      <c r="D3" s="4">
+        <f t="shared" ref="D3:D8" si="1">B3-A3</f>
+        <v>0.80849999999999955</v>
+      </c>
       <c r="E3" s="4">
         <v>7.1082000000000001</v>
       </c>
       <c r="F3" s="4">
         <v>7.883</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-    </row>
-    <row r="4" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G3" s="4">
+        <f t="shared" ref="G3:G9" si="2">E4-E3</f>
+        <v>1.2464999999999993</v>
+      </c>
+      <c r="H3" s="4">
+        <f t="shared" ref="H3:H9" si="3">F3-E3</f>
+        <v>0.77479999999999993</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4">
         <v>8.9274000000000004</v>
       </c>
       <c r="B4" s="4">
         <v>9.7359000000000009</v>
       </c>
+      <c r="C4" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2800999999999991</v>
+      </c>
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>0.80850000000000044</v>
+      </c>
       <c r="E4" s="4">
         <v>8.3546999999999993</v>
       </c>
       <c r="F4" s="4">
         <v>9.1295000000000002</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-    </row>
-    <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G4" s="4">
+        <f t="shared" si="2"/>
+        <v>1.2464000000000013</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="3"/>
+        <v>0.77480000000000082</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4">
         <v>10.2075</v>
       </c>
       <c r="B5" s="4">
         <v>10.9824</v>
       </c>
+      <c r="C5" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2127999999999997</v>
+      </c>
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>0.77490000000000059</v>
+      </c>
       <c r="E5" s="4">
         <v>9.6011000000000006</v>
       </c>
       <c r="F5" s="4">
         <v>10.375999999999999</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G5" s="4">
+        <f t="shared" si="2"/>
+        <v>1.2127999999999997</v>
+      </c>
+      <c r="H5" s="4">
+        <f t="shared" si="3"/>
+        <v>0.77489999999999881</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
         <v>11.420299999999999</v>
       </c>
       <c r="B6" s="4">
         <v>12.1951</v>
       </c>
+      <c r="C6" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2128000000000014</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>0.77480000000000082</v>
+      </c>
       <c r="E6" s="4">
         <v>10.8139</v>
       </c>
       <c r="F6" s="4">
         <v>11.588800000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G6" s="4">
+        <f t="shared" si="2"/>
+        <v>1.2127999999999997</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="3"/>
+        <v>0.77490000000000059</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4">
         <v>12.633100000000001</v>
       </c>
       <c r="B7" s="4">
         <v>13.4079</v>
       </c>
+      <c r="C7" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2127999999999997</v>
+      </c>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>0.77479999999999905</v>
+      </c>
       <c r="E7" s="4">
         <v>12.0267</v>
       </c>
       <c r="F7" s="4">
         <v>12.801500000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G7" s="4">
+        <f t="shared" si="2"/>
+        <v>1.1791</v>
+      </c>
+      <c r="H7" s="4">
+        <f t="shared" si="3"/>
+        <v>0.77480000000000082</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
         <v>13.8459</v>
       </c>
       <c r="B8" s="4">
         <v>14.620699999999999</v>
       </c>
+      <c r="C8" s="4">
+        <f t="shared" si="0"/>
+        <v>1.2463999999999995</v>
+      </c>
+      <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>0.77479999999999905</v>
+      </c>
       <c r="E8" s="4">
         <v>13.2058</v>
       </c>
       <c r="F8" s="4">
         <v>14.048</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G8" s="4">
+        <f t="shared" si="2"/>
+        <v>1.2464999999999993</v>
+      </c>
+      <c r="H8" s="4">
+        <f t="shared" si="3"/>
+        <v>0.84220000000000006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
         <v>15.0923</v>
       </c>
+      <c r="C9" s="4"/>
       <c r="E9" s="4">
         <v>14.452299999999999</v>
       </c>
       <c r="F9" s="4">
         <v>15.2608</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G9" s="4">
+        <f t="shared" si="2"/>
+        <v>1.2801000000000009</v>
+      </c>
+      <c r="H9" s="4">
+        <f t="shared" si="3"/>
+        <v>0.80850000000000044</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E10" s="4">
         <v>15.7324</v>
       </c>
@@ -587,6 +714,259 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="9.6640625" customWidth="1"/>
+    <col min="2" max="2" width="6.83203125" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="17.1640625" customWidth="1"/>
+    <col min="5" max="5" width="11" customWidth="1"/>
+    <col min="6" max="6" width="8" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" customWidth="1"/>
+    <col min="8" max="8" width="18.5" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" customWidth="1"/>
+    <col min="10" max="10" width="62.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="5"/>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="4">
+        <v>0.63280000000000003</v>
+      </c>
+      <c r="B2" s="4">
+        <v>1.1657</v>
+      </c>
+      <c r="C2" s="4">
+        <f t="shared" ref="C2:C6" si="0">A3-A2</f>
+        <v>0.96589999999999998</v>
+      </c>
+      <c r="D2" s="4">
+        <f t="shared" ref="D2:D7" si="1">B2-A2</f>
+        <v>0.53289999999999993</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0.16650000000000001</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0.73270000000000002</v>
+      </c>
+      <c r="G2" s="4">
+        <f t="shared" ref="G2:G7" si="2">E3-E2</f>
+        <v>0.99919999999999998</v>
+      </c>
+      <c r="H2" s="4">
+        <f t="shared" ref="H2:H7" si="3">F2-E2</f>
+        <v>0.56620000000000004</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="4">
+        <v>1.5987</v>
+      </c>
+      <c r="B3" s="4">
+        <v>2.0649999999999999</v>
+      </c>
+      <c r="C3" s="4">
+        <f t="shared" si="0"/>
+        <v>0.89930000000000021</v>
+      </c>
+      <c r="D3" s="4">
+        <f t="shared" si="1"/>
+        <v>0.46629999999999994</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1.1657</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1.6319999999999999</v>
+      </c>
+      <c r="G3" s="4">
+        <f t="shared" si="2"/>
+        <v>0.89929999999999999</v>
+      </c>
+      <c r="H3" s="4">
+        <f t="shared" si="3"/>
+        <v>0.46629999999999994</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="4">
+        <v>2.4980000000000002</v>
+      </c>
+      <c r="B4" s="4">
+        <v>2.9975999999999998</v>
+      </c>
+      <c r="C4" s="4">
+        <f t="shared" si="0"/>
+        <v>0.89929999999999977</v>
+      </c>
+      <c r="D4" s="4">
+        <f t="shared" si="1"/>
+        <v>0.4995999999999996</v>
+      </c>
+      <c r="E4" s="4">
+        <v>2.0649999999999999</v>
+      </c>
+      <c r="F4" s="4">
+        <v>2.5312999999999999</v>
+      </c>
+      <c r="G4" s="4">
+        <f t="shared" si="2"/>
+        <v>0.93259999999999987</v>
+      </c>
+      <c r="H4" s="4">
+        <f t="shared" si="3"/>
+        <v>0.46629999999999994</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="4">
+        <v>3.3973</v>
+      </c>
+      <c r="B5" s="4">
+        <v>3.8969</v>
+      </c>
+      <c r="C5" s="4">
+        <f t="shared" si="0"/>
+        <v>0.93260000000000032</v>
+      </c>
+      <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>0.49960000000000004</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2.9975999999999998</v>
+      </c>
+      <c r="F5" s="4">
+        <v>3.4639000000000002</v>
+      </c>
+      <c r="G5" s="4">
+        <f t="shared" si="2"/>
+        <v>0.89930000000000021</v>
+      </c>
+      <c r="H5" s="4">
+        <f t="shared" si="3"/>
+        <v>0.46630000000000038</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="4">
+        <v>4.3299000000000003</v>
+      </c>
+      <c r="B6" s="4">
+        <v>4.8628</v>
+      </c>
+      <c r="C6" s="4">
+        <f t="shared" si="0"/>
+        <v>0.96589999999999954</v>
+      </c>
+      <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>0.53289999999999971</v>
+      </c>
+      <c r="E6" s="4">
+        <v>3.8969</v>
+      </c>
+      <c r="F6" s="4">
+        <v>4.3964999999999996</v>
+      </c>
+      <c r="G6" s="4">
+        <f t="shared" si="2"/>
+        <v>0.96589999999999998</v>
+      </c>
+      <c r="H6" s="4">
+        <f t="shared" si="3"/>
+        <v>0.4995999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="4">
+        <v>5.2957999999999998</v>
+      </c>
+      <c r="B7" s="4">
+        <v>5.8287000000000004</v>
+      </c>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>0.5329000000000006</v>
+      </c>
+      <c r="E7" s="4">
+        <v>4.8628</v>
+      </c>
+      <c r="F7" s="4">
+        <v>5.3291000000000004</v>
+      </c>
+      <c r="G7" s="4">
+        <f t="shared" si="2"/>
+        <v>0.93259999999999987</v>
+      </c>
+      <c r="H7" s="4">
+        <f t="shared" si="3"/>
+        <v>0.46630000000000038</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4">
+        <v>5.7953999999999999</v>
+      </c>
+      <c r="H8" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -802,64 +1182,64 @@
       <c r="H7" s="8"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="10"/>
-      <c r="B34" s="10"/>
-      <c r="C34" s="10"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="10"/>
-      <c r="H34" s="10"/>
-      <c r="I34" s="10"/>
-      <c r="J34" s="10"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="7"/>
@@ -10503,282 +10883,75 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:J10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="9.6640625" customWidth="1"/>
-    <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="17.1640625" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.5" customWidth="1"/>
-    <col min="9" max="9" width="49.6640625" customWidth="1"/>
-  </cols>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95222076-4AF5-6B4E-A8AF-DC58D53D9681}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="4">
-        <v>7.2766999999999999</v>
-      </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="F2" s="4">
-        <v>6.6703000000000001</v>
-      </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="4">
-        <v>7.7145999999999999</v>
-      </c>
-      <c r="B3" s="4">
-        <v>8.5230999999999995</v>
-      </c>
-      <c r="C3" s="4">
-        <f t="shared" ref="C3:C8" si="0">A4-A3</f>
-        <v>1.2128000000000005</v>
-      </c>
-      <c r="D3" s="4">
-        <f t="shared" ref="D3:D8" si="1">B3-A3</f>
-        <v>0.80849999999999955</v>
-      </c>
-      <c r="E3" s="4">
-        <v>7.1082000000000001</v>
-      </c>
-      <c r="F3" s="4">
-        <v>7.883</v>
-      </c>
-      <c r="G3" s="4">
-        <f t="shared" ref="G3:G9" si="2">E4-E3</f>
-        <v>1.2464999999999993</v>
-      </c>
-      <c r="H3" s="4">
-        <f t="shared" ref="H3:H9" si="3">F3-E3</f>
-        <v>0.77479999999999993</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="4">
-        <v>8.9274000000000004</v>
-      </c>
-      <c r="B4" s="4">
-        <v>9.7359000000000009</v>
-      </c>
-      <c r="C4" s="4">
-        <f t="shared" si="0"/>
-        <v>1.2800999999999991</v>
-      </c>
-      <c r="D4" s="4">
-        <f t="shared" si="1"/>
-        <v>0.80850000000000044</v>
-      </c>
-      <c r="E4" s="4">
-        <v>8.3546999999999993</v>
-      </c>
-      <c r="F4" s="4">
-        <v>9.1295000000000002</v>
-      </c>
-      <c r="G4" s="4">
-        <f t="shared" si="2"/>
-        <v>1.2464000000000013</v>
-      </c>
-      <c r="H4" s="4">
-        <f t="shared" si="3"/>
-        <v>0.77480000000000082</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="4">
-        <v>10.2075</v>
-      </c>
-      <c r="B5" s="4">
-        <v>10.9824</v>
-      </c>
-      <c r="C5" s="4">
-        <f t="shared" si="0"/>
-        <v>1.2127999999999997</v>
-      </c>
-      <c r="D5" s="4">
-        <f t="shared" si="1"/>
-        <v>0.77490000000000059</v>
-      </c>
-      <c r="E5" s="4">
-        <v>9.6011000000000006</v>
-      </c>
-      <c r="F5" s="4">
-        <v>10.375999999999999</v>
-      </c>
-      <c r="G5" s="4">
-        <f t="shared" si="2"/>
-        <v>1.2127999999999997</v>
-      </c>
-      <c r="H5" s="4">
-        <f t="shared" si="3"/>
-        <v>0.77489999999999881</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="4">
-        <v>11.420299999999999</v>
-      </c>
-      <c r="B6" s="4">
-        <v>12.1951</v>
-      </c>
-      <c r="C6" s="4">
-        <f t="shared" si="0"/>
-        <v>1.2128000000000014</v>
-      </c>
-      <c r="D6" s="4">
-        <f t="shared" si="1"/>
-        <v>0.77480000000000082</v>
-      </c>
-      <c r="E6" s="4">
-        <v>10.8139</v>
-      </c>
-      <c r="F6" s="4">
-        <v>11.588800000000001</v>
-      </c>
-      <c r="G6" s="4">
-        <f t="shared" si="2"/>
-        <v>1.2127999999999997</v>
-      </c>
-      <c r="H6" s="4">
-        <f t="shared" si="3"/>
-        <v>0.77490000000000059</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="4">
-        <v>12.633100000000001</v>
-      </c>
-      <c r="B7" s="4">
-        <v>13.4079</v>
-      </c>
-      <c r="C7" s="4">
-        <f t="shared" si="0"/>
-        <v>1.2127999999999997</v>
-      </c>
-      <c r="D7" s="4">
-        <f t="shared" si="1"/>
-        <v>0.77479999999999905</v>
-      </c>
-      <c r="E7" s="4">
-        <v>12.0267</v>
-      </c>
-      <c r="F7" s="4">
-        <v>12.801500000000001</v>
-      </c>
-      <c r="G7" s="4">
-        <f t="shared" si="2"/>
-        <v>1.1791</v>
-      </c>
-      <c r="H7" s="4">
-        <f t="shared" si="3"/>
-        <v>0.77480000000000082</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="4">
-        <v>13.8459</v>
-      </c>
-      <c r="B8" s="4">
-        <v>14.620699999999999</v>
-      </c>
-      <c r="C8" s="4">
-        <f t="shared" si="0"/>
-        <v>1.2463999999999995</v>
-      </c>
-      <c r="D8" s="4">
-        <f t="shared" si="1"/>
-        <v>0.77479999999999905</v>
-      </c>
-      <c r="E8" s="4">
-        <v>13.2058</v>
-      </c>
-      <c r="F8" s="4">
-        <v>14.048</v>
-      </c>
-      <c r="G8" s="4">
-        <f t="shared" si="2"/>
-        <v>1.2464999999999993</v>
-      </c>
-      <c r="H8" s="4">
-        <f t="shared" si="3"/>
-        <v>0.84220000000000006</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="4">
-        <v>15.0923</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="E9" s="4">
-        <v>14.452299999999999</v>
-      </c>
-      <c r="F9" s="4">
-        <v>15.2608</v>
-      </c>
-      <c r="G9" s="4">
-        <f t="shared" si="2"/>
-        <v>1.2801000000000009</v>
-      </c>
-      <c r="H9" s="4">
-        <f t="shared" si="3"/>
-        <v>0.80850000000000044</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E10" s="4">
-        <v>15.7324</v>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="12">
+        <v>1.0674999999999999</v>
+      </c>
+      <c r="B2" s="12">
+        <v>1.2677</v>
+      </c>
+      <c r="C2" s="12">
+        <v>0.80059999999999998</v>
+      </c>
+      <c r="D2" s="12">
+        <v>0.96740000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="12">
+        <v>1.6688000000000001</v>
+      </c>
+      <c r="B3" s="12">
+        <v>1.8681000000000001</v>
+      </c>
+      <c r="C3" s="12">
+        <v>1.4011</v>
+      </c>
+      <c r="D3" s="12">
+        <v>1.5345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="12">
+        <v>2.3018000000000001</v>
+      </c>
+      <c r="B4" s="12">
+        <v>2.5019999999999998</v>
+      </c>
+      <c r="C4" s="12">
+        <v>2.0015999999999998</v>
+      </c>
+      <c r="D4" s="12">
+        <v>2.1684000000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12">
+        <v>2.6688000000000001</v>
+      </c>
+      <c r="D5" s="12">
+        <v>2.8689</v>
       </c>
     </row>
   </sheetData>
@@ -10786,7 +10959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -11017,7 +11190,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -11252,100 +11425,100 @@
       <c r="H8" s="8"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
     </row>
     <row r="999" spans="1:10" ht="13" x14ac:dyDescent="0.15">
-      <c r="A999" s="11"/>
-      <c r="B999" s="10"/>
-      <c r="C999" s="10"/>
-      <c r="D999" s="10"/>
-      <c r="E999" s="10"/>
-      <c r="F999" s="10"/>
-      <c r="G999" s="10"/>
-      <c r="H999" s="10"/>
-      <c r="I999" s="10"/>
-      <c r="J999" s="10"/>
+      <c r="A999" s="10"/>
+      <c r="B999" s="9"/>
+      <c r="C999" s="9"/>
+      <c r="D999" s="9"/>
+      <c r="E999" s="9"/>
+      <c r="F999" s="9"/>
+      <c r="G999" s="9"/>
+      <c r="H999" s="9"/>
+      <c r="I999" s="9"/>
+      <c r="J999" s="9"/>
     </row>
     <row r="1000" spans="1:10" ht="13" x14ac:dyDescent="0.15">
-      <c r="A1000" s="11"/>
-      <c r="B1000" s="10"/>
-      <c r="C1000" s="10"/>
-      <c r="D1000" s="10"/>
-      <c r="E1000" s="10"/>
-      <c r="F1000" s="10"/>
-      <c r="G1000" s="10"/>
-      <c r="H1000" s="10"/>
-      <c r="I1000" s="10"/>
-      <c r="J1000" s="10"/>
+      <c r="A1000" s="10"/>
+      <c r="B1000" s="9"/>
+      <c r="C1000" s="9"/>
+      <c r="D1000" s="9"/>
+      <c r="E1000" s="9"/>
+      <c r="F1000" s="9"/>
+      <c r="G1000" s="9"/>
+      <c r="H1000" s="9"/>
+      <c r="I1000" s="9"/>
+      <c r="J1000" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -11358,6 +11531,83 @@
     <mergeCell ref="A32:J32"/>
     <mergeCell ref="A999:J999"/>
   </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFF7C7BB-0639-B449-8409-FC4C863457C2}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="12">
+        <v>2.9666999999999999</v>
+      </c>
+      <c r="B2" s="12">
+        <v>3.2667000000000002</v>
+      </c>
+      <c r="C2" s="12">
+        <v>3.3</v>
+      </c>
+      <c r="D2" s="12">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="12">
+        <v>3.6667000000000001</v>
+      </c>
+      <c r="B3" s="12">
+        <v>3.9666999999999999</v>
+      </c>
+      <c r="C3" s="12">
+        <v>4.0332999999999997</v>
+      </c>
+      <c r="D3" s="12">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="B4" s="12">
+        <v>4.6666999999999996</v>
+      </c>
+      <c r="C4" s="12">
+        <v>4.7667000000000002</v>
+      </c>
+      <c r="D4" s="12">
+        <v>5.0332999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="12">
+        <v>5.1333000000000002</v>
+      </c>
+      <c r="B5" s="12">
+        <v>5.4</v>
+      </c>
+      <c r="C5" s="12">
+        <v>5.5</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11413,10 +11663,12 @@
       <c r="J1" s="5"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="4">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12">
         <v>0.4662</v>
       </c>
-      <c r="F2" s="4">
+      <c r="E2" s="12"/>
+      <c r="F2" s="12">
         <v>0.56610000000000005</v>
       </c>
       <c r="I2" s="4" t="s">
@@ -11424,10 +11676,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="4">
+      <c r="A3" s="12">
         <v>1.0322</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="12">
         <v>2.0312000000000001</v>
       </c>
       <c r="C3" s="4">
@@ -11438,10 +11690,10 @@
         <f t="shared" ref="D3:D10" si="1">B3-A3</f>
         <v>0.99900000000000011</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="12">
         <v>1.0322</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="12">
         <v>2.0644999999999998</v>
       </c>
       <c r="G3" s="4">
@@ -11457,10 +11709,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="4">
+      <c r="A4" s="12">
         <v>2.5972</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="12">
         <v>3.5629</v>
       </c>
       <c r="C4" s="4">
@@ -11471,10 +11723,10 @@
         <f t="shared" si="1"/>
         <v>0.9657</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="12">
         <v>2.6305000000000001</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="12">
         <v>3.5962000000000001</v>
       </c>
       <c r="G4" s="4">
@@ -11490,10 +11742,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="9">
+      <c r="A5" s="12">
         <v>4.8948</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="12">
         <v>5.7605000000000004</v>
       </c>
       <c r="C5" s="4">
@@ -11504,10 +11756,10 @@
         <f t="shared" si="1"/>
         <v>0.86570000000000036</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="12">
         <v>4.0622999999999996</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="12">
         <v>5.0279999999999996</v>
       </c>
       <c r="G5" s="4">
@@ -11520,10 +11772,10 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="9">
+      <c r="A6" s="12">
         <v>6.3932000000000002</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="12">
         <v>7.2256</v>
       </c>
       <c r="C6" s="4">
@@ -11534,10 +11786,10 @@
         <f t="shared" si="1"/>
         <v>0.83239999999999981</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="12">
         <v>5.5274000000000001</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="12">
         <v>6.4931000000000001</v>
       </c>
       <c r="G6" s="4">
@@ -11550,10 +11802,10 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="4">
+      <c r="A7" s="12">
         <v>7.5259</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="12">
         <v>7.9249000000000001</v>
       </c>
       <c r="C7" s="4">
@@ -11564,10 +11816,10 @@
         <f t="shared" si="1"/>
         <v>0.39900000000000002</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="12">
         <v>6.9926000000000004</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="12">
         <v>7.9581999999999997</v>
       </c>
       <c r="G7" s="4">
@@ -11580,10 +11832,10 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="4">
+      <c r="A8" s="12">
         <v>8.4577000000000009</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8" s="12">
         <v>9.4565999999999999</v>
       </c>
       <c r="C8" s="4">
@@ -11594,10 +11846,10 @@
         <f t="shared" si="1"/>
         <v>0.99889999999999901</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="12">
         <v>8.4909999999999997</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="12">
         <v>9.4232999999999993</v>
       </c>
       <c r="G8" s="4">
@@ -11610,10 +11862,10 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="4">
+      <c r="A9" s="12">
         <v>9.9288000000000007</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="12">
         <v>10.8218</v>
       </c>
       <c r="C9" s="4">
@@ -11624,10 +11876,10 @@
         <f t="shared" si="1"/>
         <v>0.89299999999999891</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="12">
         <v>9.9560999999999993</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="12">
         <v>10.888400000000001</v>
       </c>
       <c r="G9" s="4">
@@ -11640,20 +11892,20 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="4">
+      <c r="A10" s="12">
         <v>11.421200000000001</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10" s="12">
         <v>12.286899999999999</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="1"/>
         <v>0.86569999999999858</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="12">
         <v>11.3879</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="12">
         <v>12.286899999999999</v>
       </c>
       <c r="G10" s="4">
@@ -11666,7 +11918,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E11" s="4">
+      <c r="E11" s="12">
         <v>12.8765</v>
       </c>
     </row>
@@ -11727,7 +11979,8 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="4">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12">
         <v>0.53190000000000004</v>
       </c>
       <c r="C2" s="4">
@@ -11738,10 +11991,10 @@
         <f t="shared" ref="D2:D6" si="1">B2-A3</f>
         <v>0.49870000000000003</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="12">
         <v>0.43219999999999997</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="12">
         <v>1.0305</v>
       </c>
       <c r="G2" s="4">
@@ -11759,10 +12012,10 @@
       <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="4">
+      <c r="A3" s="12">
         <v>3.32E-2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="12">
         <v>1.5291999999999999</v>
       </c>
       <c r="C3" s="4">
@@ -11773,10 +12026,10 @@
         <f t="shared" si="1"/>
         <v>0.53169999999999984</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="12">
         <v>1.6527000000000001</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="12">
         <v>2.3161100000000001</v>
       </c>
       <c r="G3" s="4">
@@ -11794,10 +12047,10 @@
       <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="4">
+      <c r="A4" s="12">
         <v>0.99750000000000005</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4" s="12">
         <v>2.5596999999999999</v>
       </c>
       <c r="C4" s="4">
@@ -11808,10 +12061,10 @@
         <f t="shared" si="1"/>
         <v>0.56509999999999994</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="12">
         <v>2.4931999999999999</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="12">
         <v>3.0916000000000001</v>
       </c>
       <c r="G4" s="4">
@@ -11829,10 +12082,10 @@
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="4">
+      <c r="A5" s="12">
         <v>1.9945999999999999</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="12">
         <v>3.5901999999999998</v>
       </c>
       <c r="C5" s="4">
@@ -11843,10 +12096,10 @@
         <f t="shared" si="1"/>
         <v>0.53189999999999982</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="12">
         <v>3.4904999999999999</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="12">
         <v>4.1553000000000004</v>
       </c>
       <c r="G5" s="4">
@@ -11862,10 +12115,10 @@
       <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="4">
+      <c r="A6" s="12">
         <v>3.0583</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6" s="12">
         <v>4.5875000000000004</v>
       </c>
       <c r="C6" s="4">
@@ -11876,10 +12129,10 @@
         <f t="shared" si="1"/>
         <v>0.53190000000000026</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="12">
         <v>4.5542999999999996</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="12">
         <v>5.1859000000000002</v>
       </c>
       <c r="G6" s="4">
@@ -11895,17 +12148,17 @@
       <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="4">
+      <c r="A7" s="12">
         <v>4.0556000000000001</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7" s="12">
         <v>5.7178000000000004</v>
       </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="4">
+      <c r="E7" s="12">
         <v>5.5848000000000004</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="12">
         <v>6.0542999999999996</v>
       </c>
       <c r="H7" s="4">
@@ -11917,7 +12170,7 @@
       <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="4">
+      <c r="A8" s="12">
         <v>5.0861000000000001</v>
       </c>
     </row>
@@ -11976,18 +12229,20 @@
       <c r="J1" s="6"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="7">
-        <v>1.1296999999999999</v>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12">
+        <v>1.5616000000000001</v>
       </c>
       <c r="C2" s="7">
         <f t="shared" ref="C2:C5" si="0">A4-A3</f>
-        <v>0.99680000000000013</v>
+        <v>1.1629</v>
       </c>
       <c r="D2" s="7">
         <f t="shared" ref="D2:D6" si="1">B2-A3</f>
-        <v>0.56489999999999996</v>
-      </c>
-      <c r="F2" s="8">
+        <v>1.1629</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12">
         <v>0.63129999999999997</v>
       </c>
       <c r="G2" s="8">
@@ -12000,29 +12255,29 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="7">
-        <v>0.56479999999999997</v>
-      </c>
-      <c r="B3" s="7">
-        <v>1.9936</v>
+      <c r="A3" s="12">
+        <v>0.3987</v>
+      </c>
+      <c r="B3" s="12">
+        <v>2.4255</v>
       </c>
       <c r="C3" s="7">
         <f t="shared" si="0"/>
-        <v>0.83069999999999999</v>
+        <v>0.86389999999999989</v>
       </c>
       <c r="D3" s="7">
         <f t="shared" si="1"/>
-        <v>0.43199999999999994</v>
-      </c>
-      <c r="E3" s="8">
+        <v>0.86389999999999989</v>
+      </c>
+      <c r="E3" s="12">
         <v>1.0965</v>
       </c>
-      <c r="F3" s="8">
-        <v>3.2229000000000001</v>
+      <c r="F3" s="12">
+        <v>1.5616000000000001</v>
       </c>
       <c r="G3" s="8">
         <f t="shared" si="2"/>
-        <v>0.83059999999999978</v>
+        <v>0.86380000000000012</v>
       </c>
       <c r="H3" s="8">
         <f>E3-F2</f>
@@ -12033,29 +12288,29 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="7">
+      <c r="A4" s="12">
         <v>1.5616000000000001</v>
       </c>
-      <c r="B4" s="7">
-        <v>2.8574000000000002</v>
+      <c r="B4" s="12">
+        <v>3.3557999999999999</v>
       </c>
       <c r="C4" s="7">
         <f t="shared" si="0"/>
-        <v>0.89710000000000001</v>
+        <v>0.86390000000000011</v>
       </c>
       <c r="D4" s="7">
         <f t="shared" si="1"/>
-        <v>0.46510000000000007</v>
-      </c>
-      <c r="E4" s="8">
+        <v>0.9302999999999999</v>
+      </c>
+      <c r="E4" s="12">
         <v>1.9936</v>
       </c>
-      <c r="F4" s="8">
-        <v>3.9870999999999999</v>
+      <c r="F4" s="12">
+        <v>2.3923000000000001</v>
       </c>
       <c r="G4" s="8">
         <f t="shared" si="2"/>
-        <v>0.93040000000000012</v>
+        <v>0.89719999999999978</v>
       </c>
       <c r="H4" s="8"/>
       <c r="I4" s="4" t="s">
@@ -12063,11 +12318,11 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="7">
-        <v>2.3923000000000001</v>
-      </c>
-      <c r="B5" s="7">
-        <v>3.6880999999999999</v>
+      <c r="A5" s="12">
+        <v>2.4255</v>
+      </c>
+      <c r="B5" s="12">
+        <v>4.1864999999999997</v>
       </c>
       <c r="C5" s="7">
         <f t="shared" si="0"/>
@@ -12075,167 +12330,172 @@
       </c>
       <c r="D5" s="7">
         <f t="shared" si="1"/>
-        <v>0.39869999999999983</v>
-      </c>
-      <c r="E5" s="8">
-        <v>2.8241999999999998</v>
-      </c>
-      <c r="F5" s="8">
-        <v>4.9839000000000002</v>
+        <v>0.89709999999999956</v>
+      </c>
+      <c r="E5" s="12">
+        <v>2.8574000000000002</v>
+      </c>
+      <c r="F5" s="12">
+        <v>3.2562000000000002</v>
       </c>
       <c r="G5" s="8">
         <f t="shared" si="2"/>
-        <v>0.86380000000000035</v>
+        <v>0.89710000000000001</v>
       </c>
       <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="7">
+      <c r="A6" s="12">
         <v>3.2894000000000001</v>
       </c>
-      <c r="B6" s="7">
-        <v>4.4855</v>
+      <c r="B6" s="12">
+        <v>5.0835999999999997</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7">
         <f t="shared" si="1"/>
-        <v>0.29900000000000038</v>
-      </c>
-      <c r="E6" s="8">
+        <v>0.89710000000000001</v>
+      </c>
+      <c r="E6" s="12">
         <v>3.7545999999999999</v>
       </c>
-      <c r="F6" s="8">
-        <v>5.4880000000000004</v>
+      <c r="F6" s="12">
+        <v>4.1532999999999998</v>
       </c>
       <c r="G6" s="8">
         <f t="shared" si="2"/>
-        <v>0.89710000000000001</v>
+        <v>0.86380000000000035</v>
       </c>
       <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="7">
+      <c r="A7" s="12">
         <v>4.1864999999999997</v>
       </c>
-      <c r="B7" s="7">
-        <v>5.3826000000000001</v>
+      <c r="B7" s="12">
+        <v>5.5488</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="8">
-        <v>4.6184000000000003</v>
-      </c>
-      <c r="F7" s="8"/>
+      <c r="E7" s="12">
+        <v>4.6516999999999999</v>
+      </c>
+      <c r="F7" s="12">
+        <v>5.0503999999999998</v>
+      </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
+      <c r="A8" s="12">
+        <v>5.0835999999999997</v>
+      </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="8">
+      <c r="E8" s="12">
         <v>5.5155000000000003</v>
       </c>
-      <c r="F8" s="8"/>
+      <c r="F8" s="12">
+        <v>5.5488</v>
+      </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="10"/>
-      <c r="B30" s="10"/>
-      <c r="C30" s="10"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="10"/>
-      <c r="B31" s="10"/>
-      <c r="C31" s="10"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="10"/>
-      <c r="B32" s="10"/>
-      <c r="C32" s="10"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="7"/>
@@ -21903,6 +22163,86 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5AFD87E-BD9B-1B4B-87F3-651ECD2D6A1E}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A2" s="12">
+        <v>1.887</v>
+      </c>
+      <c r="B2" s="12">
+        <v>0.79249999999999998</v>
+      </c>
+      <c r="C2" s="12">
+        <v>0.82550000000000001</v>
+      </c>
+      <c r="D2" s="12">
+        <v>0.60229999999999995</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A3" s="12">
+        <v>1.8821000000000001</v>
+      </c>
+      <c r="B3" s="12">
+        <v>1.4198999999999999</v>
+      </c>
+      <c r="C3" s="12">
+        <v>1.4859</v>
+      </c>
+      <c r="D3" s="12">
+        <v>1.0896999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A4" s="12">
+        <v>2.6086</v>
+      </c>
+      <c r="B4" s="12">
+        <v>2.0802</v>
+      </c>
+      <c r="C4" s="12">
+        <v>2.2122999999999999</v>
+      </c>
+      <c r="D4" s="12">
+        <v>1.75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A5" s="12">
+        <v>3.2090000000000001</v>
+      </c>
+      <c r="B5" s="12">
+        <v>2.8397000000000001</v>
+      </c>
+      <c r="C5" s="12">
+        <v>2.8727</v>
+      </c>
+      <c r="D5" s="12">
+        <v>2.4434999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -22148,257 +22488,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-  </sheetPr>
-  <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="9.6640625" customWidth="1"/>
-    <col min="2" max="2" width="6.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="17.1640625" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="8" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" customWidth="1"/>
-    <col min="8" max="8" width="18.5" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" customWidth="1"/>
-    <col min="10" max="10" width="62.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="4">
-        <v>0.63280000000000003</v>
-      </c>
-      <c r="B2" s="4">
-        <v>1.1657</v>
-      </c>
-      <c r="C2" s="4">
-        <f t="shared" ref="C2:C6" si="0">A3-A2</f>
-        <v>0.96589999999999998</v>
-      </c>
-      <c r="D2" s="4">
-        <f t="shared" ref="D2:D7" si="1">B2-A2</f>
-        <v>0.53289999999999993</v>
-      </c>
-      <c r="E2" s="4">
-        <v>0.16650000000000001</v>
-      </c>
-      <c r="F2" s="4">
-        <v>0.73270000000000002</v>
-      </c>
-      <c r="G2" s="4">
-        <f t="shared" ref="G2:G7" si="2">E3-E2</f>
-        <v>0.99919999999999998</v>
-      </c>
-      <c r="H2" s="4">
-        <f t="shared" ref="H2:H7" si="3">F2-E2</f>
-        <v>0.56620000000000004</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="4">
-        <v>1.5987</v>
-      </c>
-      <c r="B3" s="4">
-        <v>2.0649999999999999</v>
-      </c>
-      <c r="C3" s="4">
-        <f t="shared" si="0"/>
-        <v>0.89930000000000021</v>
-      </c>
-      <c r="D3" s="4">
-        <f t="shared" si="1"/>
-        <v>0.46629999999999994</v>
-      </c>
-      <c r="E3" s="4">
-        <v>1.1657</v>
-      </c>
-      <c r="F3" s="4">
-        <v>1.6319999999999999</v>
-      </c>
-      <c r="G3" s="4">
-        <f t="shared" si="2"/>
-        <v>0.89929999999999999</v>
-      </c>
-      <c r="H3" s="4">
-        <f t="shared" si="3"/>
-        <v>0.46629999999999994</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="4">
-        <v>2.4980000000000002</v>
-      </c>
-      <c r="B4" s="4">
-        <v>2.9975999999999998</v>
-      </c>
-      <c r="C4" s="4">
-        <f t="shared" si="0"/>
-        <v>0.89929999999999977</v>
-      </c>
-      <c r="D4" s="4">
-        <f t="shared" si="1"/>
-        <v>0.4995999999999996</v>
-      </c>
-      <c r="E4" s="4">
-        <v>2.0649999999999999</v>
-      </c>
-      <c r="F4" s="4">
-        <v>2.5312999999999999</v>
-      </c>
-      <c r="G4" s="4">
-        <f t="shared" si="2"/>
-        <v>0.93259999999999987</v>
-      </c>
-      <c r="H4" s="4">
-        <f t="shared" si="3"/>
-        <v>0.46629999999999994</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="4">
-        <v>3.3973</v>
-      </c>
-      <c r="B5" s="4">
-        <v>3.8969</v>
-      </c>
-      <c r="C5" s="4">
-        <f t="shared" si="0"/>
-        <v>0.93260000000000032</v>
-      </c>
-      <c r="D5" s="4">
-        <f t="shared" si="1"/>
-        <v>0.49960000000000004</v>
-      </c>
-      <c r="E5" s="4">
-        <v>2.9975999999999998</v>
-      </c>
-      <c r="F5" s="4">
-        <v>3.4639000000000002</v>
-      </c>
-      <c r="G5" s="4">
-        <f t="shared" si="2"/>
-        <v>0.89930000000000021</v>
-      </c>
-      <c r="H5" s="4">
-        <f t="shared" si="3"/>
-        <v>0.46630000000000038</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="4">
-        <v>4.3299000000000003</v>
-      </c>
-      <c r="B6" s="4">
-        <v>4.8628</v>
-      </c>
-      <c r="C6" s="4">
-        <f t="shared" si="0"/>
-        <v>0.96589999999999954</v>
-      </c>
-      <c r="D6" s="4">
-        <f t="shared" si="1"/>
-        <v>0.53289999999999971</v>
-      </c>
-      <c r="E6" s="4">
-        <v>3.8969</v>
-      </c>
-      <c r="F6" s="4">
-        <v>4.3964999999999996</v>
-      </c>
-      <c r="G6" s="4">
-        <f t="shared" si="2"/>
-        <v>0.96589999999999998</v>
-      </c>
-      <c r="H6" s="4">
-        <f t="shared" si="3"/>
-        <v>0.4995999999999996</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="4">
-        <v>5.2957999999999998</v>
-      </c>
-      <c r="B7" s="4">
-        <v>5.8287000000000004</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4">
-        <f t="shared" si="1"/>
-        <v>0.5329000000000006</v>
-      </c>
-      <c r="E7" s="4">
-        <v>4.8628</v>
-      </c>
-      <c r="F7" s="4">
-        <v>5.3291000000000004</v>
-      </c>
-      <c r="G7" s="4">
-        <f t="shared" si="2"/>
-        <v>0.93259999999999987</v>
-      </c>
-      <c r="H7" s="4">
-        <f t="shared" si="3"/>
-        <v>0.46630000000000038</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4">
-        <v>5.7953999999999999</v>
-      </c>
-      <c r="H8" s="4"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/TT2026 Walking Quantification.xlsx
+++ b/TT2026 Walking Quantification.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ithacaedu-my.sharepoint.com/personal/iwoods_ithaca_edu/Documents/Desktop/tarditracks/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="11_E05EFDE08085FF9075DE2FBF335F4849B20072D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DF3AC3C-6AB2-4645-AE86-413FC7B9466E}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="11_E05EFDE08085FF9075DE2FBF335F4849B20072D0" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5601F615-6230-3948-A4B2-A20CE9FCBEB3}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="40360" windowHeight="17760" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="40360" windowHeight="17760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Group1 - slow walk" sheetId="2" r:id="rId1"/>
     <sheet name="Group1 - fast walk" sheetId="3" r:id="rId2"/>
     <sheet name="Group1 - slow run" sheetId="4" r:id="rId3"/>
-    <sheet name="Group 1 - fast run" sheetId="11" r:id="rId4"/>
+    <sheet name="Group1 - fast run" sheetId="11" r:id="rId4"/>
     <sheet name="Group2 - slow walk" sheetId="5" r:id="rId5"/>
     <sheet name="Group2 - fast walk" sheetId="6" r:id="rId6"/>
     <sheet name="Group2 - slow run" sheetId="7" r:id="rId7"/>
@@ -213,10 +213,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -232,6 +232,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1182,64 +1186,64 @@
       <c r="H7" s="8"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
     </row>
     <row r="33" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="9"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="9"/>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-      <c r="H33" s="9"/>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
     </row>
     <row r="34" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="9"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
-      <c r="H34" s="9"/>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
     </row>
     <row r="38" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="7"/>
@@ -10889,68 +10893,68 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" s="12">
+      <c r="A2" s="10">
         <v>1.0674999999999999</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>1.2677</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="10">
         <v>0.80059999999999998</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="10">
         <v>0.96740000000000004</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>1.6688000000000001</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="10">
         <v>1.8681000000000001</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="10">
         <v>1.4011</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="10">
         <v>1.5345</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>2.3018000000000001</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="10">
         <v>2.5019999999999998</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="10">
         <v>2.0015999999999998</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="10">
         <v>2.1684000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10">
         <v>2.6688000000000001</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="10">
         <v>2.8689</v>
       </c>
     </row>
@@ -11425,100 +11429,100 @@
       <c r="H8" s="8"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
     </row>
     <row r="999" spans="1:10" ht="13" x14ac:dyDescent="0.15">
-      <c r="A999" s="10"/>
-      <c r="B999" s="9"/>
-      <c r="C999" s="9"/>
-      <c r="D999" s="9"/>
-      <c r="E999" s="9"/>
-      <c r="F999" s="9"/>
-      <c r="G999" s="9"/>
-      <c r="H999" s="9"/>
-      <c r="I999" s="9"/>
-      <c r="J999" s="9"/>
+      <c r="A999" s="11"/>
+      <c r="B999" s="12"/>
+      <c r="C999" s="12"/>
+      <c r="D999" s="12"/>
+      <c r="E999" s="12"/>
+      <c r="F999" s="12"/>
+      <c r="G999" s="12"/>
+      <c r="H999" s="12"/>
+      <c r="I999" s="12"/>
+      <c r="J999" s="12"/>
     </row>
     <row r="1000" spans="1:10" ht="13" x14ac:dyDescent="0.15">
-      <c r="A1000" s="10"/>
-      <c r="B1000" s="9"/>
-      <c r="C1000" s="9"/>
-      <c r="D1000" s="9"/>
-      <c r="E1000" s="9"/>
-      <c r="F1000" s="9"/>
-      <c r="G1000" s="9"/>
-      <c r="H1000" s="9"/>
-      <c r="I1000" s="9"/>
-      <c r="J1000" s="9"/>
+      <c r="A1000" s="11"/>
+      <c r="B1000" s="12"/>
+      <c r="C1000" s="12"/>
+      <c r="D1000" s="12"/>
+      <c r="E1000" s="12"/>
+      <c r="F1000" s="12"/>
+      <c r="G1000" s="12"/>
+      <c r="H1000" s="12"/>
+      <c r="I1000" s="12"/>
+      <c r="J1000" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -11541,69 +11545,69 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" s="12">
+      <c r="A2" s="10">
         <v>2.9666999999999999</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>3.2667000000000002</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="10">
         <v>3.3</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="10">
         <v>3.6</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>3.6667000000000001</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="10">
         <v>3.9666999999999999</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="10">
         <v>4.0332999999999997</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="10">
         <v>4.3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>4.4000000000000004</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="10">
         <v>4.6666999999999996</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="10">
         <v>4.7667000000000002</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="10">
         <v>5.0332999999999997</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>5.1333000000000002</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>5.4</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <v>5.5</v>
       </c>
     </row>
@@ -11663,12 +11667,12 @@
       <c r="J1" s="5"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10">
         <v>0.4662</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10">
         <v>0.56610000000000005</v>
       </c>
       <c r="I2" s="4" t="s">
@@ -11676,10 +11680,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>1.0322</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="10">
         <v>2.0312000000000001</v>
       </c>
       <c r="C3" s="4">
@@ -11690,10 +11694,10 @@
         <f t="shared" ref="D3:D10" si="1">B3-A3</f>
         <v>0.99900000000000011</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="10">
         <v>1.0322</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="10">
         <v>2.0644999999999998</v>
       </c>
       <c r="G3" s="4">
@@ -11709,10 +11713,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>2.5972</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="10">
         <v>3.5629</v>
       </c>
       <c r="C4" s="4">
@@ -11723,10 +11727,10 @@
         <f t="shared" si="1"/>
         <v>0.9657</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="10">
         <v>2.6305000000000001</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="10">
         <v>3.5962000000000001</v>
       </c>
       <c r="G4" s="4">
@@ -11742,10 +11746,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>4.8948</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>5.7605000000000004</v>
       </c>
       <c r="C5" s="4">
@@ -11756,10 +11760,10 @@
         <f t="shared" si="1"/>
         <v>0.86570000000000036</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <v>4.0622999999999996</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="10">
         <v>5.0279999999999996</v>
       </c>
       <c r="G5" s="4">
@@ -11772,10 +11776,10 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="12">
+      <c r="A6" s="10">
         <v>6.3932000000000002</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="10">
         <v>7.2256</v>
       </c>
       <c r="C6" s="4">
@@ -11786,10 +11790,10 @@
         <f t="shared" si="1"/>
         <v>0.83239999999999981</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>5.5274000000000001</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="10">
         <v>6.4931000000000001</v>
       </c>
       <c r="G6" s="4">
@@ -11802,10 +11806,10 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>7.5259</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="10">
         <v>7.9249000000000001</v>
       </c>
       <c r="C7" s="4">
@@ -11816,10 +11820,10 @@
         <f t="shared" si="1"/>
         <v>0.39900000000000002</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="10">
         <v>6.9926000000000004</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="10">
         <v>7.9581999999999997</v>
       </c>
       <c r="G7" s="4">
@@ -11832,10 +11836,10 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="12">
+      <c r="A8" s="10">
         <v>8.4577000000000009</v>
       </c>
-      <c r="B8" s="12">
+      <c r="B8" s="10">
         <v>9.4565999999999999</v>
       </c>
       <c r="C8" s="4">
@@ -11846,10 +11850,10 @@
         <f t="shared" si="1"/>
         <v>0.99889999999999901</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="10">
         <v>8.4909999999999997</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="10">
         <v>9.4232999999999993</v>
       </c>
       <c r="G8" s="4">
@@ -11862,10 +11866,10 @@
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="12">
+      <c r="A9" s="10">
         <v>9.9288000000000007</v>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="10">
         <v>10.8218</v>
       </c>
       <c r="C9" s="4">
@@ -11876,10 +11880,10 @@
         <f t="shared" si="1"/>
         <v>0.89299999999999891</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="10">
         <v>9.9560999999999993</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="10">
         <v>10.888400000000001</v>
       </c>
       <c r="G9" s="4">
@@ -11892,20 +11896,20 @@
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="12">
+      <c r="A10" s="10">
         <v>11.421200000000001</v>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="10">
         <v>12.286899999999999</v>
       </c>
       <c r="D10" s="4">
         <f t="shared" si="1"/>
         <v>0.86569999999999858</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="10">
         <v>11.3879</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="10">
         <v>12.286899999999999</v>
       </c>
       <c r="G10" s="4">
@@ -11918,7 +11922,7 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E11" s="12">
+      <c r="E11" s="10">
         <v>12.8765</v>
       </c>
     </row>
@@ -11979,8 +11983,8 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10">
         <v>0.53190000000000004</v>
       </c>
       <c r="C2" s="4">
@@ -11991,10 +11995,10 @@
         <f t="shared" ref="D2:D6" si="1">B2-A3</f>
         <v>0.49870000000000003</v>
       </c>
-      <c r="E2" s="12">
+      <c r="E2" s="10">
         <v>0.43219999999999997</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="10">
         <v>1.0305</v>
       </c>
       <c r="G2" s="4">
@@ -12012,10 +12016,10 @@
       <c r="K2" s="4"/>
     </row>
     <row r="3" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>3.32E-2</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="10">
         <v>1.5291999999999999</v>
       </c>
       <c r="C3" s="4">
@@ -12026,10 +12030,10 @@
         <f t="shared" si="1"/>
         <v>0.53169999999999984</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="10">
         <v>1.6527000000000001</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="10">
         <v>2.3161100000000001</v>
       </c>
       <c r="G3" s="4">
@@ -12047,10 +12051,10 @@
       <c r="K3" s="4"/>
     </row>
     <row r="4" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>0.99750000000000005</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="10">
         <v>2.5596999999999999</v>
       </c>
       <c r="C4" s="4">
@@ -12061,10 +12065,10 @@
         <f t="shared" si="1"/>
         <v>0.56509999999999994</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="10">
         <v>2.4931999999999999</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="10">
         <v>3.0916000000000001</v>
       </c>
       <c r="G4" s="4">
@@ -12082,10 +12086,10 @@
       <c r="K4" s="4"/>
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>1.9945999999999999</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>3.5901999999999998</v>
       </c>
       <c r="C5" s="4">
@@ -12096,10 +12100,10 @@
         <f t="shared" si="1"/>
         <v>0.53189999999999982</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <v>3.4904999999999999</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="10">
         <v>4.1553000000000004</v>
       </c>
       <c r="G5" s="4">
@@ -12115,10 +12119,10 @@
       <c r="K5" s="4"/>
     </row>
     <row r="6" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="12">
+      <c r="A6" s="10">
         <v>3.0583</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="10">
         <v>4.5875000000000004</v>
       </c>
       <c r="C6" s="4">
@@ -12129,10 +12133,10 @@
         <f t="shared" si="1"/>
         <v>0.53190000000000026</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>4.5542999999999996</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="10">
         <v>5.1859000000000002</v>
       </c>
       <c r="G6" s="4">
@@ -12148,17 +12152,17 @@
       <c r="K6" s="4"/>
     </row>
     <row r="7" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>4.0556000000000001</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="10">
         <v>5.7178000000000004</v>
       </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="12">
+      <c r="E7" s="10">
         <v>5.5848000000000004</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="10">
         <v>6.0542999999999996</v>
       </c>
       <c r="H7" s="4">
@@ -12170,7 +12174,7 @@
       <c r="K7" s="4"/>
     </row>
     <row r="8" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="12">
+      <c r="A8" s="10">
         <v>5.0861000000000001</v>
       </c>
     </row>
@@ -12229,8 +12233,8 @@
       <c r="J1" s="6"/>
     </row>
     <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12">
+      <c r="A2" s="10"/>
+      <c r="B2" s="10">
         <v>1.5616000000000001</v>
       </c>
       <c r="C2" s="7">
@@ -12241,8 +12245,8 @@
         <f t="shared" ref="D2:D6" si="1">B2-A3</f>
         <v>1.1629</v>
       </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12">
+      <c r="E2" s="10"/>
+      <c r="F2" s="10">
         <v>0.63129999999999997</v>
       </c>
       <c r="G2" s="8">
@@ -12255,10 +12259,10 @@
       </c>
     </row>
     <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>0.3987</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="10">
         <v>2.4255</v>
       </c>
       <c r="C3" s="7">
@@ -12269,10 +12273,10 @@
         <f t="shared" si="1"/>
         <v>0.86389999999999989</v>
       </c>
-      <c r="E3" s="12">
+      <c r="E3" s="10">
         <v>1.0965</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="10">
         <v>1.5616000000000001</v>
       </c>
       <c r="G3" s="8">
@@ -12288,10 +12292,10 @@
       </c>
     </row>
     <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>1.5616000000000001</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="10">
         <v>3.3557999999999999</v>
       </c>
       <c r="C4" s="7">
@@ -12302,10 +12306,10 @@
         <f t="shared" si="1"/>
         <v>0.9302999999999999</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="10">
         <v>1.9936</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="10">
         <v>2.3923000000000001</v>
       </c>
       <c r="G4" s="8">
@@ -12318,10 +12322,10 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>2.4255</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>4.1864999999999997</v>
       </c>
       <c r="C5" s="7">
@@ -12332,10 +12336,10 @@
         <f t="shared" si="1"/>
         <v>0.89709999999999956</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="10">
         <v>2.8574000000000002</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="10">
         <v>3.2562000000000002</v>
       </c>
       <c r="G5" s="8">
@@ -12345,10 +12349,10 @@
       <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="12">
+      <c r="A6" s="10">
         <v>3.2894000000000001</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="10">
         <v>5.0835999999999997</v>
       </c>
       <c r="C6" s="7"/>
@@ -12356,10 +12360,10 @@
         <f t="shared" si="1"/>
         <v>0.89710000000000001</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="10">
         <v>3.7545999999999999</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="10">
         <v>4.1532999999999998</v>
       </c>
       <c r="G6" s="8">
@@ -12369,133 +12373,133 @@
       <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="12">
+      <c r="A7" s="10">
         <v>4.1864999999999997</v>
       </c>
-      <c r="B7" s="12">
+      <c r="B7" s="10">
         <v>5.5488</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
-      <c r="E7" s="12">
+      <c r="E7" s="10">
         <v>4.6516999999999999</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="10">
         <v>5.0503999999999998</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="12">
+      <c r="A8" s="10">
         <v>5.0835999999999997</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
-      <c r="E8" s="12">
+      <c r="E8" s="10">
         <v>5.5155000000000003</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="10">
         <v>5.5488</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
     <row r="25" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="9"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="9"/>
-      <c r="E25" s="9"/>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
     </row>
     <row r="26" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="9"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="9"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="9"/>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
     </row>
     <row r="27" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="9"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
     </row>
     <row r="28" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="9"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="9"/>
-      <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
     </row>
     <row r="29" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="9"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="9"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="9"/>
-      <c r="E30" s="9"/>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="H30" s="9"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
     </row>
     <row r="31" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="9"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
     </row>
     <row r="32" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="9"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="9"/>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-      <c r="H32" s="9"/>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="7"/>
@@ -22168,72 +22172,72 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A2" s="12">
+      <c r="A2" s="10">
         <v>1.887</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>0.79249999999999998</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="10">
         <v>0.82550000000000001</v>
       </c>
-      <c r="D2" s="12">
+      <c r="D2" s="10">
         <v>0.60229999999999995</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A3" s="12">
+      <c r="A3" s="10">
         <v>1.8821000000000001</v>
       </c>
-      <c r="B3" s="12">
+      <c r="B3" s="10">
         <v>1.4198999999999999</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="10">
         <v>1.4859</v>
       </c>
-      <c r="D3" s="12">
+      <c r="D3" s="10">
         <v>1.0896999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A4" s="12">
+      <c r="A4" s="10">
         <v>2.6086</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="10">
         <v>2.0802</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="10">
         <v>2.2122999999999999</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="10">
         <v>1.75</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A5" s="12">
+      <c r="A5" s="10">
         <v>3.2090000000000001</v>
       </c>
-      <c r="B5" s="12">
+      <c r="B5" s="10">
         <v>2.8397000000000001</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="10">
         <v>2.8727</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="10">
         <v>2.4434999999999998</v>
       </c>
     </row>
